--- a/survey_templates/018_care_coordination_effectiveness_survey--survey_templates.xlsx
+++ b/survey_templates/018_care_coordination_effectiveness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -947,8 +947,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -976,12 +976,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'patient',_'value':_'patient'}</t>
+          <t>patient</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Patient', 'value': 'patient'}</t>
+          <t>Patient</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'family_member/caregiver',_'value':_'caregiver'}</t>
+          <t>family_member/caregiver</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Family Member/Caregiver', 'value': 'caregiver'}</t>
+          <t>Family Member/Caregiver</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'healthcare_provider/staff',_'value':_'provider'}</t>
+          <t>healthcare_provider/staff</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Healthcare Provider/Staff', 'value': 'provider'}</t>
+          <t>Healthcare Provider/Staff</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'care_manager',_'value':_'care_manager'}</t>
+          <t>care_manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Care Manager', 'value': 'care_manager'}</t>
+          <t>Care Manager</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_am_open_to_it',_'value':_true}</t>
+          <t>yes,_i_am_open_to_it</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I am open to it', 'value': True}</t>
+          <t>Yes, I am open to it</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'no,_please_do_not_contact_me',_'value':_false}</t>
+          <t>no,_please_do_not_contact_me</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'No, please do not contact me', 'value': False}</t>
+          <t>No, please do not contact me</t>
         </is>
       </c>
     </row>
